--- a/platform_PiN_output/South_Sudan___SSD/PiN_results_South_Sudan___SSD_1020_01PM.xlsx
+++ b/platform_PiN_output/South_Sudan___SSD/PiN_results_South_Sudan___SSD_1020_01PM.xlsx
@@ -17868,7 +17868,7 @@
       </c>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>20/10/2025 13:38</t>
+          <t>20/10/2025 13:56</t>
         </is>
       </c>
     </row>
